--- a/data/trans_dic/IMC_inf_MED_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado</t>
+          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,34; 61,15</t>
+          <t>41,73; 61,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36,66; 62,94</t>
+          <t>35,39; 62,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,37; 72,16</t>
+          <t>20,72; 70,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39,93; 61,76</t>
+          <t>39,68; 61,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,47; 64,59</t>
+          <t>40,25; 64,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,37; 58,31</t>
+          <t>22,04; 57,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,77; 58,59</t>
+          <t>43,59; 58,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,03; 59,12</t>
+          <t>42,67; 60,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,71; 57,53</t>
+          <t>28,56; 59,25</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,4; 49,54</t>
+          <t>40,47; 49,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,75; 38,89</t>
+          <t>30,7; 39,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,64; 32,15</t>
+          <t>15,02; 32,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49,86; 58,71</t>
+          <t>50,5; 59,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,1; 48,65</t>
+          <t>40,14; 48,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,83; 52,31</t>
+          <t>39,15; 52,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,82; 53,16</t>
+          <t>46,5; 52,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,04; 42,77</t>
+          <t>36,91; 42,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,34; 42,25</t>
+          <t>28,52; 41,63</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,31; 49,62</t>
+          <t>34,21; 49,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,85; 36,71</t>
+          <t>22,57; 36,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,14; 37,63</t>
+          <t>19,25; 37,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44,69; 60,9</t>
+          <t>45,76; 60,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37,52; 52,34</t>
+          <t>37,65; 52,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,86; 39,32</t>
+          <t>20,16; 38,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,55; 53,29</t>
+          <t>41,91; 53,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,66; 43,23</t>
+          <t>32,6; 43,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,09; 35,61</t>
+          <t>22,71; 35,43</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,41; 48,75</t>
+          <t>41,02; 48,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,35; 38,04</t>
+          <t>31,4; 38,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,75; 33,34</t>
+          <t>18,79; 34,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50,18; 57,08</t>
+          <t>50,25; 57,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,91; 48,97</t>
+          <t>41,6; 48,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,95; 46,67</t>
+          <t>36,08; 46,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,98; 52,07</t>
+          <t>46,99; 52,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,67; 42,87</t>
+          <t>37,96; 42,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,93; 38,98</t>
+          <t>29,9; 39,06</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>33671</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18887</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9526</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28777</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>25968</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10667</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>62448</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>44856</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>20192</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>27504; 40566</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13624; 24038</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4382; 14979</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22575; 35088</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>19735; 31414</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5899; 15363</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>53526; 71698</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>37348; 52513</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>13683; 28387</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>141822</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>117401</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>43545</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>189136</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>157923</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97386</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>330958</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>275323</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>140931</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>128192; 156620</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>103412; 131640</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>26261; 56932</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>175007; 205021</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>142956; 173331</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>83789; 112147</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>308418; 350253</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>255757; 295933</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>110916; 161902</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>50021</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33198</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18987</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>63003</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>53910</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>21807</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>113024</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>87108</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>40794</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>40367; 58474</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>25250; 40387</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12982; 25218</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>54522; 72384</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>44843; 62511</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>15231; 29248</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>99394; 125921</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>75289; 99901</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>32470; 50655</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>225514</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>169486</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>72058</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>280916</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>237801</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>129860</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>506431</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>407287</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>201918</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>205390; 243812</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>152963; 186468</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>49501; 89587</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>262627; 300503</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>218058; 256355</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>114136; 147287</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>480784; 532438</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>383953; 434542</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>173328; 226453</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IMC_inf_MED_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición) (tasa de respuesta: 68,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,73; 61,55</t>
+          <t>41,22; 60,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,39; 62,44</t>
+          <t>36,3; 61,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,72; 70,83</t>
+          <t>21,82; 73,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39,68; 61,67</t>
+          <t>38,8; 61,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,25; 64,07</t>
+          <t>40,19; 64,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,04; 57,4</t>
+          <t>23,22; 56,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,59; 58,38</t>
+          <t>43,57; 57,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,67; 60,0</t>
+          <t>42,48; 60,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,56; 59,25</t>
+          <t>28,91; 57,97</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,47; 49,44</t>
+          <t>40,19; 49,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,7; 39,08</t>
+          <t>30,89; 39,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,02; 32,56</t>
+          <t>13,74; 31,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50,5; 59,16</t>
+          <t>49,68; 59,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,14; 48,67</t>
+          <t>39,58; 48,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,15; 52,4</t>
+          <t>39,17; 52,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,5; 52,8</t>
+          <t>46,74; 53,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,91; 42,71</t>
+          <t>36,83; 42,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,52; 41,63</t>
+          <t>28,39; 41,98</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,21; 49,55</t>
+          <t>34,73; 50,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,57; 36,1</t>
+          <t>22,95; 36,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,25; 37,4</t>
+          <t>20,45; 38,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45,76; 60,75</t>
+          <t>45,26; 60,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37,65; 52,49</t>
+          <t>36,92; 52,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,16; 38,71</t>
+          <t>20,56; 38,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,91; 53,1</t>
+          <t>41,93; 53,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,6; 43,25</t>
+          <t>32,09; 42,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,71; 35,43</t>
+          <t>22,33; 35,43</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,02; 48,7</t>
+          <t>41,87; 48,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,4; 38,27</t>
+          <t>31,07; 38,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,79; 34,01</t>
+          <t>19,67; 33,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50,25; 57,5</t>
+          <t>50,15; 57,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,6; 48,9</t>
+          <t>41,9; 49,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,08; 46,56</t>
+          <t>35,56; 46,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,99; 52,03</t>
+          <t>46,88; 51,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,96; 42,96</t>
+          <t>37,74; 42,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,9; 39,06</t>
+          <t>29,16; 38,91</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición) (tasa de respuesta: 68,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27504; 40566</t>
+          <t>27164; 39745</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13624; 24038</t>
+          <t>13975; 23720</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4382; 14979</t>
+          <t>4614; 15464</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22575; 35088</t>
+          <t>22080; 34776</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19735; 31414</t>
+          <t>19707; 31384</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5899; 15363</t>
+          <t>6215; 15238</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53526; 71698</t>
+          <t>53510; 71131</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37348; 52513</t>
+          <t>37183; 53155</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13683; 28387</t>
+          <t>13848; 27775</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>128192; 156620</t>
+          <t>127316; 156016</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>103412; 131640</t>
+          <t>104049; 131737</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26261; 56932</t>
+          <t>24023; 55723</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>175007; 205021</t>
+          <t>172165; 204686</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>142956; 173331</t>
+          <t>140937; 172868</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83789; 112147</t>
+          <t>83832; 113310</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>308418; 350253</t>
+          <t>310001; 352093</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>255757; 295933</t>
+          <t>255235; 297436</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>110916; 161902</t>
+          <t>110410; 163246</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>40367; 58474</t>
+          <t>40977; 59009</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25250; 40387</t>
+          <t>25683; 40753</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12982; 25218</t>
+          <t>13788; 26008</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54522; 72384</t>
+          <t>53924; 71593</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44843; 62511</t>
+          <t>43972; 62251</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15231; 29248</t>
+          <t>15538; 28832</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99394; 125921</t>
+          <t>99438; 125865</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>75289; 99901</t>
+          <t>74110; 99098</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32470; 50655</t>
+          <t>31931; 50661</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>205390; 243812</t>
+          <t>209635; 244360</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>152963; 186468</t>
+          <t>151353; 186167</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49501; 89587</t>
+          <t>51821; 88127</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>262627; 300503</t>
+          <t>262075; 300743</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>218058; 256355</t>
+          <t>219625; 259167</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>114136; 147287</t>
+          <t>112479; 147517</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>480784; 532438</t>
+          <t>479685; 531049</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>383953; 434542</t>
+          <t>381664; 432825</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>173328; 226453</t>
+          <t>169064; 225589</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_inf_MED_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>50,58%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>52,96%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>42,83%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>51,09%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>49,06%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>45,04%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>50,58%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>52,96%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>37,14%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,22; 60,31</t>
+          <t>39,93; 61,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36,3; 61,61</t>
+          <t>41,47; 64,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,82; 73,13</t>
+          <t>24,36; 61,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,8; 61,12</t>
+          <t>41,34; 61,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,19; 64,01</t>
+          <t>36,66; 62,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,22; 56,93</t>
+          <t>12,32; 49,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,57; 57,92</t>
+          <t>43,77; 58,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,48; 60,73</t>
+          <t>42,03; 59,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,91; 57,97</t>
+          <t>24,59; 49,78</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>54,58%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>44,35%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>45,09%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>44,77%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>34,86%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>24,9%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54,58%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>44,35%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>37,54%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,19; 49,25</t>
+          <t>49,86; 58,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,89; 39,11</t>
+          <t>40,1; 48,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,74; 31,87</t>
+          <t>38,94; 51,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49,68; 59,06</t>
+          <t>40,4; 49,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,58; 48,54</t>
+          <t>30,75; 38,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,17; 52,95</t>
+          <t>22,34; 33,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,74; 53,08</t>
+          <t>46,82; 53,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,83; 42,93</t>
+          <t>37,04; 42,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,39; 41,98</t>
+          <t>32,98; 42,45</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>52,88%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>45,27%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>29,12%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>42,39%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>29,67%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>28,16%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>52,88%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>45,27%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,73; 50,01</t>
+          <t>44,69; 60,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,95; 36,42</t>
+          <t>37,52; 52,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,45; 38,57</t>
+          <t>20,91; 40,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45,26; 60,09</t>
+          <t>34,31; 49,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,92; 52,27</t>
+          <t>22,85; 36,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,56; 38,16</t>
+          <t>19,34; 37,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,93; 53,07</t>
+          <t>42,55; 53,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,09; 42,9</t>
+          <t>32,66; 43,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,33; 35,43</t>
+          <t>22,31; 35,87</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>53,75%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>45,36%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>41,09%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>45,04%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>34,79%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>27,35%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>53,75%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>45,36%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,87; 48,81</t>
+          <t>50,18; 57,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,07; 38,21</t>
+          <t>41,91; 48,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,67; 33,45</t>
+          <t>35,96; 46,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50,15; 57,55</t>
+          <t>41,41; 48,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,9; 49,44</t>
+          <t>31,35; 38,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,56; 46,63</t>
+          <t>23,63; 33,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,88; 51,9</t>
+          <t>46,98; 52,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,74; 42,79</t>
+          <t>37,67; 42,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,16; 38,91</t>
+          <t>31,65; 39,16</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28777</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25968</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10504</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>33671</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>18887</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9526</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28777</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>25968</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20192</t>
+          <t>15286</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27164; 39745</t>
+          <t>22718; 35138</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13975; 23720</t>
+          <t>20331; 31667</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4614; 15464</t>
+          <t>5973; 15103</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22080; 34776</t>
+          <t>27248; 40298</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19707; 31384</t>
+          <t>14113; 24231</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6215; 15238</t>
+          <t>2050; 8215</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53510; 71131</t>
+          <t>53750; 71956</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37183; 53155</t>
+          <t>36791; 51743</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13848; 27775</t>
+          <t>10119; 20489</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>173</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>67</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>189136</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>157923</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>90308</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>141822</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>117401</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>43545</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>189136</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>157923</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97386</t>
+          <t>41625</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>140931</t>
+          <t>131933</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>127316; 156016</t>
+          <t>172783; 203462</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>104049; 131737</t>
+          <t>142794; 173241</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24023; 55723</t>
+          <t>77992; 103921</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>172165; 204686</t>
+          <t>127965; 156919</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>140937; 172868</t>
+          <t>103558; 130982</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83832; 113310</t>
+          <t>33770; 51387</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>310001; 352093</t>
+          <t>310542; 352639</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>255235; 297436</t>
+          <t>256653; 296342</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>110410; 163246</t>
+          <t>115930; 149213</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>63003</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>53910</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>20526</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>50021</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>33198</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18987</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>63003</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>53910</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21807</t>
+          <t>19177</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40794</t>
+          <t>39704</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>40977; 59009</t>
+          <t>53247; 72559</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25683; 40753</t>
+          <t>44688; 62339</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13788; 26008</t>
+          <t>14738; 28201</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53924; 71593</t>
+          <t>40484; 58550</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>43972; 62251</t>
+          <t>25571; 41073</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15538; 28832</t>
+          <t>13133; 25508</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99438; 125865</t>
+          <t>100912; 126367</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>74110; 99098</t>
+          <t>75439; 99843</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31931; 50661</t>
+          <t>30881; 49642</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>322</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>252</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>103</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>280916</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>237801</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>121338</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>225514</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>169486</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>72058</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>280916</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>237801</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>129860</t>
+          <t>65584</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>201918</t>
+          <t>186922</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>209635; 244360</t>
+          <t>262228; 298309</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>151353; 186167</t>
+          <t>219700; 256707</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51821; 88127</t>
+          <t>106201; 137074</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>262075; 300743</t>
+          <t>207320; 244101</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>219625; 259167</t>
+          <t>152738; 185334</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>112479; 147517</t>
+          <t>55698; 77825</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>479685; 531049</t>
+          <t>480780; 532812</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>381664; 432825</t>
+          <t>380987; 433598</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>169064; 225589</t>
+          <t>168051; 207975</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_inf_MED_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Estudios-trans_dic.xlsx
@@ -532,7 +532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 71,23%)</t>
+          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,31 +632,31 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.5057636434845424</v>
+        <v>0.4657047840377311</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.5296484093670114</v>
+        <v>0.4733691316374324</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>0.4283132414053943</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.5108885031659872</v>
+        <v>0.4871716962160342</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.4905947447069675</v>
+        <v>0.4512596848107593</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.2874581888136999</v>
+        <v>0.3394098336947229</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.5085140087609992</v>
+        <v>0.4767676386070236</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.5124708767998072</v>
+        <v>0.4636459037373108</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0.3713878380120911</v>
+        <v>0.3891872659764399</v>
       </c>
     </row>
     <row r="5">
@@ -667,31 +667,31 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.3992703373934586</v>
+        <v>0.3738704411589819</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.4146697507084505</v>
+        <v>0.3689566924164793</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0.2435612045645529</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.4134386743246361</v>
+        <v>0.3984615763744734</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.366585972655227</v>
+        <v>0.3375204866703637</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.1232325215070014</v>
+        <v>0.1817387800216397</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.4376841180034391</v>
+        <v>0.4186628126681232</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.420339162270703</v>
+        <v>0.3948897732198366</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.2458659376193398</v>
+        <v>0.2604932304688486</v>
       </c>
     </row>
     <row r="6">
@@ -702,31 +702,31 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.6175504828726796</v>
+        <v>0.5618481108522054</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.6458917090408312</v>
+        <v>0.5762673198246888</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0.615804472185444</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.6114507222405522</v>
+        <v>0.5860758036078983</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.6293835203234641</v>
+        <v>0.5641362080345921</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.4938848386225054</v>
+        <v>0.5394077808159854</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.5859388457435649</v>
+        <v>0.548137984756752</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.5911640538473062</v>
+        <v>0.5412119063833678</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>0.497823901825025</v>
+        <v>0.5151146372893112</v>
       </c>
     </row>
     <row r="7">
@@ -741,31 +741,31 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.5457758279679681</v>
+        <v>0.5288261011105012</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.4434780684965542</v>
+        <v>0.446121492495118</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.4508648717003198</v>
+        <v>0.4505337471229794</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.4477258520522747</v>
+        <v>0.4481518797374033</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.3485609237881442</v>
+        <v>0.3321748983861199</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.2753096060346892</v>
+        <v>0.2799202359770341</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.4989522486006108</v>
+        <v>0.4902498350798606</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.3973403085441015</v>
+        <v>0.3912254068836856</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.3753509216328321</v>
+        <v>0.3769677900730277</v>
       </c>
     </row>
     <row r="8">
@@ -776,31 +776,31 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.4985858357537655</v>
+        <v>0.4884726317490961</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.4009943101353013</v>
+        <v>0.4077392790505151</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.3893745757252551</v>
+        <v>0.3870645591171803</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.4039784387775912</v>
+        <v>0.4084147113164016</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.307463408877546</v>
+        <v>0.2946248570397408</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.2233552493095119</v>
+        <v>0.2293369764653288</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.4681725396638418</v>
+        <v>0.4616966675203141</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.370395872894372</v>
+        <v>0.3641833167292576</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.3298213534140829</v>
+        <v>0.3351453587264898</v>
       </c>
     </row>
     <row r="9">
@@ -811,31 +811,31 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.5871143020206953</v>
+        <v>0.566484741474269</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.4864952246019911</v>
+        <v>0.4858178254580534</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.5188279183165703</v>
+        <v>0.5158936975028418</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.4953870135130423</v>
+        <v>0.4895421731203441</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.3888838022173372</v>
+        <v>0.3717998226084171</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.3398777164637389</v>
+        <v>0.3463762434009742</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.5316385238231466</v>
+        <v>0.5228675090506922</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.4276749228253662</v>
+        <v>0.419727571570486</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.4245125976524962</v>
+        <v>0.4266296342804237</v>
       </c>
     </row>
     <row r="10">
@@ -850,31 +850,31 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.5287758699899939</v>
+        <v>0.5232379028152686</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.4526753684648693</v>
+        <v>0.4498624569845496</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.2911882347834991</v>
+        <v>0.2931784537622616</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.4238992612917087</v>
+        <v>0.425288711245244</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.2967169911154996</v>
+        <v>0.3246826454932012</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.2824521057614933</v>
+        <v>0.285345629030913</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.4765906773035776</v>
+        <v>0.474164682737844</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.3771292933865585</v>
+        <v>0.3895786213191445</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.2869020507514308</v>
+        <v>0.2894145600858432</v>
       </c>
     </row>
     <row r="11">
@@ -885,31 +885,31 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.4468941344762113</v>
+        <v>0.4484472320135177</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.375239643893201</v>
+        <v>0.3838557482730113</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.2090772560643392</v>
+        <v>0.2111694037037786</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.3430737642995509</v>
+        <v>0.3492546652281304</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.2285482297549793</v>
+        <v>0.2628371095954423</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.1934223425456829</v>
+        <v>0.2058439243160959</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.4255142362790962</v>
+        <v>0.4245555509442357</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.3266068475178979</v>
+        <v>0.3433220820121992</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.2231466658670435</v>
+        <v>0.2251823057845045</v>
       </c>
     </row>
     <row r="12">
@@ -920,31 +920,31 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.6089818007262321</v>
+        <v>0.59345741107797</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.5234489568835711</v>
+        <v>0.5148366581811065</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.4000584632053732</v>
+        <v>0.3986180673461889</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.4961753097062224</v>
+        <v>0.4914338170092301</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.3671028069818897</v>
+        <v>0.3934404726362971</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.3756970424642503</v>
+        <v>0.3800790150750876</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.5328506220746122</v>
+        <v>0.5241744617539472</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.4322635554912911</v>
+        <v>0.4350975976311745</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.3587204073974344</v>
+        <v>0.3620247346169958</v>
       </c>
     </row>
     <row r="13">
@@ -959,31 +959,31 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.537543462276809</v>
+        <v>0.5199400016870342</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.4536268504821084</v>
+        <v>0.4498187677890572</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.410877839109871</v>
+        <v>0.4106948042901157</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.4504246060940044</v>
+        <v>0.4480993812094337</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.3478785913841982</v>
+        <v>0.3410060676206463</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.2782241723445429</v>
+        <v>0.2860584886184616</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.4949172686288911</v>
+        <v>0.484873638188347</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.4026881249815326</v>
+        <v>0.3978428558400455</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.3519941824153193</v>
+        <v>0.3552752365535039</v>
       </c>
     </row>
     <row r="14">
@@ -994,31 +994,31 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.5017821531525133</v>
+        <v>0.4879897249629671</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.4190984251942523</v>
+        <v>0.4154058591283558</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.3596202801771443</v>
+        <v>0.360849822429133</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.4140860597102639</v>
+        <v>0.4136218620576</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.3135019948392222</v>
+        <v>0.3095667519334427</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.2362883060635219</v>
+        <v>0.2397956487304755</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.4698499865824892</v>
+        <v>0.4608995178659543</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.3766850554496688</v>
+        <v>0.3739540851910583</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.3164587096881991</v>
+        <v>0.3205643724097117</v>
       </c>
     </row>
     <row r="15">
@@ -1029,31 +1029,31 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.5708256033739203</v>
+        <v>0.5507766005825726</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.4896927445480223</v>
+        <v>0.4813556038517585</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.4641609216140092</v>
+        <v>0.4680858711282094</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.4875489171772106</v>
+        <v>0.4818713526649803</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.3804068958485285</v>
+        <v>0.3720579677346967</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.3301576549105049</v>
+        <v>0.3336870490922481</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.5206986646598036</v>
+        <v>0.5079631143775496</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.4287020752950155</v>
+        <v>0.4196961487405965</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.3916401595218164</v>
+        <v>0.3932631680112414</v>
       </c>
     </row>
     <row r="16">
@@ -1103,7 +1103,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 71,23%)</t>
+          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1203,31 +1203,31 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -1238,31 +1238,31 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>28777</v>
+        <v>35288</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>25968</v>
+        <v>31007</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>10504</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>33671</v>
+        <v>39252</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>18887</v>
+        <v>23203</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>4782</v>
+        <v>6543</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>62448</v>
+        <v>74539</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>44856</v>
+        <v>54210</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>15286</v>
+        <v>17047</v>
       </c>
     </row>
     <row r="6">
@@ -1273,31 +1273,31 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>22718</v>
+        <v>28329</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>20331</v>
+        <v>24167</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>5973</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>27248</v>
+        <v>32104</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>14113</v>
+        <v>17355</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>2050</v>
+        <v>3503</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>53750</v>
+        <v>65455</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>36791</v>
+        <v>46171</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>10119</v>
+        <v>11410</v>
       </c>
     </row>
     <row r="7">
@@ -1308,31 +1308,31 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>35138</v>
+        <v>42573</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>31667</v>
+        <v>37747</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>15103</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>40298</v>
+        <v>47221</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>24231</v>
+        <v>29007</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>8215</v>
+        <v>10398</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>71956</v>
+        <v>85698</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>51743</v>
+        <v>63279</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>20489</v>
+        <v>22563</v>
       </c>
     </row>
     <row r="8">
@@ -1347,31 +1347,31 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>273</v>
+        <v>312</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>223</v>
+        <v>264</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>476</v>
+        <v>553</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>396</v>
+        <v>457</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">
@@ -1382,31 +1382,31 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>189136</v>
+        <v>217419</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>157923</v>
+        <v>186908</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>90308</v>
+        <v>94790</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>141822</v>
+        <v>168837</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>117401</v>
+        <v>129378</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>41625</v>
+        <v>44644</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>330958</v>
+        <v>386256</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>275323</v>
+        <v>316286</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>131933</v>
+        <v>139435</v>
       </c>
     </row>
     <row r="10">
@@ -1417,31 +1417,31 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>172783</v>
+        <v>200828</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>142794</v>
+        <v>170828</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>77992</v>
+        <v>81437</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>127965</v>
+        <v>153867</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>103558</v>
+        <v>114753</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>33770</v>
+        <v>36577</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>310542</v>
+        <v>363760</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>256653</v>
+        <v>294424</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>115930</v>
+        <v>123965</v>
       </c>
     </row>
     <row r="11">
@@ -1452,31 +1452,31 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>203462</v>
+        <v>232902</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>173241</v>
+        <v>203540</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>103921</v>
+        <v>108542</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>156919</v>
+        <v>184431</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>130982</v>
+        <v>144811</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>51387</v>
+        <v>55243</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>352639</v>
+        <v>411955</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>296342</v>
+        <v>339329</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>149213</v>
+        <v>157804</v>
       </c>
     </row>
     <row r="12">
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="E12" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="H12" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="F12" s="6" t="n">
-        <v>70</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>29</v>
-      </c>
       <c r="I12" s="6" t="n">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -1526,31 +1526,31 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>63003</v>
+        <v>72373</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>53910</v>
+        <v>66146</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>20526</v>
+        <v>21989</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>50021</v>
+        <v>59062</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>33198</v>
+        <v>44347</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>19177</v>
+        <v>19797</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>113024</v>
+        <v>131436</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>87108</v>
+        <v>110493</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>39704</v>
+        <v>41787</v>
       </c>
     </row>
     <row r="14">
@@ -1561,31 +1561,31 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>53247</v>
+        <v>62028</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>44688</v>
+        <v>56440</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>14738</v>
+        <v>15838</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>40484</v>
+        <v>48503</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>25571</v>
+        <v>35900</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>13133</v>
+        <v>14281</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>100912</v>
+        <v>117684</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>75439</v>
+        <v>97373</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>30881</v>
+        <v>32512</v>
       </c>
     </row>
     <row r="15">
@@ -1596,31 +1596,31 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>72559</v>
+        <v>82086</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>62339</v>
+        <v>75699</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>28201</v>
+        <v>29898</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>58550</v>
+        <v>68248</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>41073</v>
+        <v>53738</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>25508</v>
+        <v>26370</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>126367</v>
+        <v>145298</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>99843</v>
+        <v>123403</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>49642</v>
+        <v>52270</v>
       </c>
     </row>
     <row r="16">
@@ -1635,31 +1635,31 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>403</v>
+        <v>462</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>338</v>
+        <v>404</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>725</v>
+        <v>843</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>590</v>
+        <v>699</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>271</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17">
@@ -1670,31 +1670,31 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>280916</v>
+        <v>325079</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>237801</v>
+        <v>284061</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>121338</v>
+        <v>127284</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>225514</v>
+        <v>267151</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>169486</v>
+        <v>196928</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>65584</v>
+        <v>70984</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>506431</v>
+        <v>592231</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>407287</v>
+        <v>480989</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>186922</v>
+        <v>198268</v>
       </c>
     </row>
     <row r="18">
@@ -1705,31 +1705,31 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>262228</v>
+        <v>305103</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>219700</v>
+        <v>262329</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>106201</v>
+        <v>111836</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>207320</v>
+        <v>246596</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>152738</v>
+        <v>178772</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>55698</v>
+        <v>59504</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>480780</v>
+        <v>562949</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>380987</v>
+        <v>452108</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>168051</v>
+        <v>178897</v>
       </c>
     </row>
     <row r="19">
@@ -1740,31 +1740,31 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>298309</v>
+        <v>344359</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>256707</v>
+        <v>303976</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>137074</v>
+        <v>145071</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>244101</v>
+        <v>287286</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>185334</v>
+        <v>214860</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>77825</v>
+        <v>82803</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>532812</v>
+        <v>620433</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>433598</v>
+        <v>507410</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>207975</v>
+        <v>219468</v>
       </c>
     </row>
     <row r="20">
